--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:46</t>
+    <t xml:space="preserve">2026-09-09 23:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:46</t>
+    <t xml:space="preserve">2026-09-18 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:34</t>
+    <t xml:space="preserve">2026-09-23 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:07</t>
+    <t xml:space="preserve">2026-10-02 15:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:22</t>
+    <t xml:space="preserve">2026-10-05 13:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -866,7 +866,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>117207.62</v>
+        <v>117207.63</v>
       </c>
     </row>
     <row r="20">
